--- a/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_leaf_membership.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/cluster_classifier/tables/mrt_leaf_membership.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -567,73 +567,73 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>065C</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -643,17 +643,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>077B</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,7 +663,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>078B</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,7 +673,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,57 +683,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>097ABC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>098C</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t xml:space="preserve">111C </t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>117ABC</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -743,17 +743,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -763,17 +763,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -783,27 +783,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>141B</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>146B</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>150B</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -813,137 +813,137 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -953,7 +953,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -963,61 +963,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
